--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2536,17 +2536,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>406</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>.182</t>
+          <t>.180</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -2571,22 +2571,22 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>.295</t>
+          <t>.296</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>.371</t>
+          <t>.367</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>.666</t>
+          <t>.663</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -2613,17 +2613,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>145</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>465</t>
+          <t>469</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>.219</t>
+          <t>.217</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2648,22 +2648,22 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>.285</t>
+          <t>.283</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>.409</t>
+          <t>.405</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>.694</t>
+          <t>.688</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -2767,17 +2767,17 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>135</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>.296</t>
+          <t>.294</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -2802,22 +2802,22 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>.421</t>
+          <t>.418</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>.546</t>
+          <t>.542</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>.967</t>
+          <t>.960</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -2844,17 +2844,17 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>76</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>271</t>
+          <t>275</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>.232</t>
+          <t>.233</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -2879,22 +2879,22 @@
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>.314</t>
+          <t>.313</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>.358</t>
+          <t>.356</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>.672</t>
+          <t>.669</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3954,32 +3954,32 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>114.1</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/12/2026 12:45</t>
+          <t>09/13/2026 13:44</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>406</t>
+          <t>411</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -2571,22 +2571,22 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>.296</t>
+          <t>.295</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>.367</t>
+          <t>.365</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>.663</t>
+          <t>.660</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -2613,17 +2613,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>146</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>473</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>.217</t>
+          <t>.216</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2648,22 +2648,22 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>.283</t>
+          <t>.281</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>.405</t>
+          <t>.402</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>.688</t>
+          <t>.683</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -2767,17 +2767,17 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>136</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>503</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>.294</t>
+          <t>.292</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -2802,22 +2802,22 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>.418</t>
+          <t>.417</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>.542</t>
+          <t>.539</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>.960</t>
+          <t>.956</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -2844,17 +2844,17 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>77</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>279</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>.233</t>
+          <t>.229</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -2874,27 +2874,27 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>.313</t>
+          <t>.311</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>.356</t>
+          <t>.351</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>.669</t>
+          <t>.662</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -3646,17 +3646,17 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -4237,12 +4237,12 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -4262,22 +4262,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>101.1</t>
+          <t>103.1</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.14</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>111</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/13/2026 13:44</t>
+          <t>09/14/2026 15:48</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2536,32 +2536,32 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>415</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>.180</t>
+          <t>.181</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -2571,22 +2571,22 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>.295</t>
+          <t>.294</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>.365</t>
+          <t>.371</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>.660</t>
+          <t>.665</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -3723,17 +3723,17 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2.74</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/14/2026 15:48</t>
+          <t>09/15/2026 14:15</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2536,17 +2536,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>419</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>.181</t>
+          <t>.179</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -2571,22 +2571,22 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>.294</t>
+          <t>.292</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>.371</t>
+          <t>.368</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>.665</t>
+          <t>.660</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -2613,17 +2613,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>147</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>476</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>.216</t>
+          <t>.214</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2648,22 +2648,22 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>.281</t>
+          <t>.279</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>.402</t>
+          <t>.399</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>.683</t>
+          <t>.678</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -2767,17 +2767,17 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>137</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>505</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>.292</t>
+          <t>.291</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>107</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -2807,17 +2807,17 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>.539</t>
+          <t>.537</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>.956</t>
+          <t>.954</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/15/2026 14:15</t>
+          <t>09/16/2026 14:08</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2536,17 +2536,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>422</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>.179</t>
+          <t>.182</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -2571,22 +2571,22 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>.292</t>
+          <t>.295</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>.368</t>
+          <t>.372</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>.660</t>
+          <t>.667</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -2613,17 +2613,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>148</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>478</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>.214</t>
+          <t>.213</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2648,22 +2648,22 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>.279</t>
+          <t>.278</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>.399</t>
+          <t>.397</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>.678</t>
+          <t>.675</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -2767,17 +2767,17 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>138</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>508</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>.291</t>
+          <t>.289</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>103</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -2802,22 +2802,22 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>.417</t>
+          <t>.414</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>.537</t>
+          <t>.533</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>.954</t>
+          <t>.947</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -3723,17 +3723,17 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3775,17 +3775,17 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -3800,22 +3800,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>172.1</t>
+          <t>178.1</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -3954,17 +3954,17 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>118.2</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>4.32</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/16/2026 14:08</t>
+          <t>09/17/2026 14:12</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -2613,17 +2613,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>481</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>.213</t>
+          <t>.212</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -2653,17 +2653,17 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>.397</t>
+          <t>.395</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>.675</t>
+          <t>.673</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -2690,17 +2690,17 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>118</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>352</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>.218</t>
+          <t>.219</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -2710,12 +2710,12 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -2725,22 +2725,22 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>.304</t>
+          <t>.306</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>.292</t>
+          <t>.293</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>.596</t>
+          <t>.599</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -3646,17 +3646,17 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -4083,14 +4083,14 @@
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -4108,12 +4108,12 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>4.78</t>
+          <t>4.73</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/17/2026 14:12</t>
+          <t>09/18/2026 13:30</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2536,17 +2536,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>119</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>426</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>.182</t>
+          <t>.181</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -2571,22 +2571,22 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>.295</t>
+          <t>.293</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>.372</t>
+          <t>.369</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>.667</t>
+          <t>.662</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -2690,17 +2690,17 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>119</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>353</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>.219</t>
+          <t>.218</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>.306</t>
+          <t>.307</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>.293</t>
+          <t>.292</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -2767,17 +2767,17 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>140</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>518</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>.289</t>
+          <t>.288</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>104</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>108</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -2802,22 +2802,22 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>.414</t>
+          <t>.411</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>.533</t>
+          <t>.529</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>.947</t>
+          <t>.940</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -3954,32 +3954,32 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>118.2</t>
+          <t>120.1</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>4.32</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>121</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -4006,17 +4006,17 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>77</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/18/2026 13:30</t>
+          <t>09/19/2026 12:59</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2536,32 +2536,32 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>430</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>.181</t>
+          <t>.184</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -2571,22 +2571,22 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>.293</t>
+          <t>.294</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>.369</t>
+          <t>.379</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>.662</t>
+          <t>.673</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -2613,17 +2613,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>150</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>485</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>.212</t>
+          <t>.210</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2648,22 +2648,22 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>.278</t>
+          <t>.276</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>.395</t>
+          <t>.392</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>.673</t>
+          <t>.668</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -2690,12 +2690,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>354</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -2725,22 +2725,22 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>.307</t>
+          <t>.306</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>.292</t>
+          <t>.291</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>.599</t>
+          <t>.597</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>141</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>518</t>
+          <t>523</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>.288</t>
+          <t>.287</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>107</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>109</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -2802,22 +2802,22 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>.411</t>
+          <t>.409</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>.529</t>
+          <t>.532</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>.940</t>
+          <t>.941</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>57</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -3646,22 +3646,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/19/2026 12:59</t>
+          <t>09/20/2026 13:31</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2536,17 +2536,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>121</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>433</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>.184</t>
+          <t>.182</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>.379</t>
+          <t>.376</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>.673</t>
+          <t>.670</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -2613,17 +2613,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>151</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>485</t>
+          <t>489</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>.210</t>
+          <t>.209</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2648,22 +2648,22 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>.276</t>
+          <t>.274</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>.392</t>
+          <t>.389</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>.668</t>
+          <t>.663</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -2690,17 +2690,17 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>121</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>357</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>.218</t>
+          <t>.216</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -2725,22 +2725,22 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>.306</t>
+          <t>.304</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>.291</t>
+          <t>.289</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>.597</t>
+          <t>.593</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -3723,17 +3723,17 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/20/2026 13:31</t>
+          <t>09/21/2026 15:47</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/21/2026 15:47</t>
+          <t>09/22/2026 13:57</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2536,17 +2536,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>436</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>.182</t>
+          <t>.181</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>.376</t>
+          <t>.374</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>.670</t>
+          <t>.668</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -2613,12 +2613,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>152</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>494</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>.274</t>
+          <t>.273</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -2658,12 +2658,12 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>.663</t>
+          <t>.662</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -2690,17 +2690,17 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>361</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>.216</t>
+          <t>.222</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -2710,12 +2710,12 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -2725,22 +2725,22 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>.304</t>
+          <t>.308</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>.289</t>
+          <t>.294</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>.593</t>
+          <t>.602</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>59.0</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -3661,17 +3661,17 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -3775,12 +3775,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>178.1</t>
+          <t>183.1</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
@@ -3815,17 +3815,17 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>186</t>
+          <t>191</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>48</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/22/2026 13:57</t>
+          <t>09/23/2026 14:09</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2536,17 +2536,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>440</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>.181</t>
+          <t>.180</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -2571,22 +2571,22 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>.294</t>
+          <t>.293</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>.374</t>
+          <t>.370</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>.668</t>
+          <t>.663</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -2613,17 +2613,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>153</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>494</t>
+          <t>496</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>.209</t>
+          <t>.208</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2653,17 +2653,17 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>.389</t>
+          <t>.387</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>.662</t>
+          <t>.660</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/23/2026 14:09</t>
+          <t>09/24/2026 14:07</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2536,17 +2536,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>442</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>.180</t>
+          <t>.179</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>.293</t>
+          <t>.294</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>.370</t>
+          <t>.369</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -2613,12 +2613,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>154</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>500</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -2653,17 +2653,17 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>.387</t>
+          <t>.386</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>.660</t>
+          <t>.659</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -2690,17 +2690,17 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>364</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>.222</t>
+          <t>.223</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -2725,22 +2725,22 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>.308</t>
+          <t>.310</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>.294</t>
+          <t>.297</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>.602</t>
+          <t>.607</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>59</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -3631,7 +3631,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -3646,22 +3646,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>59.0</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -3954,32 +3954,32 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>120.1</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>123</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>44</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/24/2026 14:07</t>
+          <t>09/25/2026 14:31</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -2613,32 +2613,32 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>155</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>503</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>.208</t>
+          <t>.209</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -2648,22 +2648,22 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>.273</t>
+          <t>.275</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>.386</t>
+          <t>.392</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>.659</t>
+          <t>.667</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -3723,17 +3723,17 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/25/2026 14:31</t>
+          <t>09/26/2026 13:42</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2536,17 +2536,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>446</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>.179</t>
+          <t>.177</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -2571,22 +2571,22 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>.294</t>
+          <t>.293</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>.369</t>
+          <t>.365</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>.663</t>
+          <t>.658</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -2613,17 +2613,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>156</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>506</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>.209</t>
+          <t>.208</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2638,32 +2638,32 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>66</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>.275</t>
+          <t>.276</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>.392</t>
+          <t>.389</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>.667</t>
+          <t>.665</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -2690,17 +2690,17 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>124</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>369</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>.223</t>
+          <t>.222</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>.310</t>
+          <t>.309</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>.297</t>
+          <t>.298</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/26/2026 13:42</t>
+          <t>09/27/2026 14:37</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2536,17 +2536,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>126</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>451</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>.177</t>
+          <t>.182</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -2571,22 +2571,22 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>.293</t>
+          <t>.296</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>.365</t>
+          <t>.368</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>.658</t>
+          <t>.664</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -2613,17 +2613,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>157</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>506</t>
+          <t>510</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>.208</t>
+          <t>.210</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -2648,22 +2648,22 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>.276</t>
+          <t>.279</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>.389</t>
+          <t>.390</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>.665</t>
+          <t>.669</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -3775,12 +3775,12 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -3800,32 +3800,32 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>183.1</t>
+          <t>186.1</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>193</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -3949,27 +3949,27 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>124.2</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>4.19</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>125</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/27/2026 14:37</t>
+          <t>09/28/2026 17:30</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/28/2026 17:30</t>
+          <t>09/29/2026 15:34</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/29/2026 15:34</t>
+          <t>09/30/2026 15:47</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>09/30/2026 15:47</t>
+          <t>10/01/2026 16:12</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/01/2026 16:12</t>
+          <t>10/02/2026 15:35</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/02/2026 15:35</t>
+          <t>10/03/2026 14:12</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/03/2026 14:12</t>
+          <t>10/04/2026 14:42</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/04/2026 14:42</t>
+          <t>10/05/2026 18:10</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/05/2026 18:10</t>
+          <t>10/06/2026 15:46</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/06/2026 15:46</t>
+          <t>10/07/2026 16:14</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/07/2026 16:14</t>
+          <t>10/08/2026 16:14</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/08/2026 16:14</t>
+          <t>10/09/2026 15:58</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/09/2026 15:58</t>
+          <t>10/10/2026 15:08</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/10/2026 15:08</t>
+          <t>10/11/2026 15:29</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/11/2026 15:29</t>
+          <t>10/12/2026 18:48</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/12/2026 18:48</t>
+          <t>10/13/2026 16:49</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/13/2026 16:49</t>
+          <t>10/14/2026 14:25</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/14/2026 14:25</t>
+          <t>10/15/2026 14:03</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/15/2026 14:03</t>
+          <t>10/16/2026 13:51</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/16/2026 13:51</t>
+          <t>10/17/2026 12:48</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/17/2026 12:48</t>
+          <t>10/18/2026 13:06</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/18/2026 13:06</t>
+          <t>10/19/2026 16:20</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/19/2026 16:20</t>
+          <t>10/20/2026 14:12</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/20/2026 14:12</t>
+          <t>10/21/2026 14:24</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/21/2026 14:24</t>
+          <t>10/22/2026 14:26</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/22/2026 14:26</t>
+          <t>10/23/2026 14:08</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/23/2026 14:08</t>
+          <t>10/24/2026 13:11</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/24/2026 13:11</t>
+          <t>10/25/2026 13:38</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/25/2026 13:38</t>
+          <t>10/26/2026 15:59</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/26/2026 15:59</t>
+          <t>10/27/2026 15:13</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/27/2026 15:13</t>
+          <t>10/28/2026 15:49</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/28/2026 15:49</t>
+          <t>10/29/2026 15:58</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/29/2026 15:58</t>
+          <t>10/30/2026 15:44</t>
         </is>
       </c>
     </row>

--- a/noles_in_the_pros.xlsx
+++ b/noles_in_the_pros.xlsx
@@ -2586,7 +2586,7 @@
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -3048,7 +3048,7 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3825,7 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -4133,7 +4133,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4441,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>10/30/2026 15:44</t>
+          <t>10/31/2026 15:11</t>
         </is>
       </c>
     </row>
